--- a/HISPEC_allsubs.xlsx
+++ b/HISPEC_allsubs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashleybaker/Documents/HISPEC/ThroughputBudget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95A076C-5B5C-2544-A687-1E777D6BEF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1952D28-24A5-0645-B34C-62BD00BA9024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="-24860" windowWidth="34680" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20200" yWindow="-23980" windowWidth="26040" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <author>tc={7F1D9F1A-5EC9-6C43-BCC4-B706F903AA15}</author>
   </authors>
   <commentList>
-    <comment ref="F112" authorId="0" shapeId="0" xr:uid="{56141629-55F1-1446-BFB4-120BC87945C5}">
+    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{56141629-55F1-1446-BFB4-120BC87945C5}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -50,7 +50,7 @@
     Update this to LGS option</t>
       </text>
     </comment>
-    <comment ref="C119" authorId="1" shapeId="0" xr:uid="{7F1D9F1A-5EC9-6C43-BCC4-B706F903AA15}">
+    <comment ref="C120" authorId="1" shapeId="0" xr:uid="{7F1D9F1A-5EC9-6C43-BCC4-B706F903AA15}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="228">
   <si>
     <t>Include?</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Secondary Obscuration</t>
   </si>
   <si>
-    <t>Keck Blue Book (page 4-8)</t>
-  </si>
-  <si>
     <t>AO</t>
   </si>
   <si>
@@ -311,18 +308,12 @@
     <t>https://caltech.sharepoint.com/:p:/r/sites/coo/hispec/_layouts/15/Doc.aspx?sourcedoc=%7BE4638353-8CCD-4B06-A6EA-914174FB0D58%7D&amp;file=FEI_OpticalDesignNotes_DD.pptx&amp;nav=eyJzSWQiOjM0OCwiY0lkIjoyNjMwMzYyODI5fQ&amp;action=edit&amp;mobileredirect=true</t>
   </si>
   <si>
-    <t>N-LAK22</t>
-  </si>
-  <si>
     <t>glass\N-LAK22_internal_transmittance.csv</t>
   </si>
   <si>
     <t>Edmun lens #47-317 - COTS achromatic doublet: Surface 1 -  N-LAK22 14.5mm CT</t>
   </si>
   <si>
-    <t>N-SF6</t>
-  </si>
-  <si>
     <t>glass\N-SF6_internal_transmittance.csv</t>
   </si>
   <si>
@@ -338,18 +329,12 @@
     <t>See PO#39-S662182 report from vendor - Ravg &lt; 1% over ATC bandpass. Could put in full curve but feeling lazy</t>
   </si>
   <si>
-    <t>BSL7Y</t>
-  </si>
-  <si>
     <t>glass\BSL7Y_internal_transmittance.csv</t>
   </si>
   <si>
     <t>ohara, Note Norland 61 is bond material - not included here</t>
   </si>
   <si>
-    <t>Cleartran</t>
-  </si>
-  <si>
     <t>glass\cleartran_transmission.csv</t>
   </si>
   <si>
@@ -419,9 +404,6 @@
     <t>CSD Dichroic Reflection</t>
   </si>
   <si>
-    <t>coatings\Asahi\Final transmission model(Channel splitting dichroic)_reflection.csv</t>
-  </si>
-  <si>
     <t>No AR coating bc blue arm sees only the reflection off CSD - UPDATE TODO with new angle sim</t>
   </si>
   <si>
@@ -488,9 +470,6 @@
     <t>CSD Dichroic Transmission</t>
   </si>
   <si>
-    <t>coatings\Asahi\Final transmission model(Channel splitting dichroic)_transmission.csv</t>
-  </si>
-  <si>
     <t>TODO -  swap with simulations because we accidentally ordered this at wrong operating angle</t>
   </si>
   <si>
@@ -723,6 +702,51 @@
   </si>
   <si>
     <t>Goddard data - 1 % lower, assuming 18713</t>
+  </si>
+  <si>
+    <t>coatings\Asahi\CSD_model_28deg_reflection.csv</t>
+  </si>
+  <si>
+    <t>coatings\Asahi\CSD_model_28deg_transmission.csv</t>
+  </si>
+  <si>
+    <t>coatings\Asahi\CSD_model_45deg_reflection.csv</t>
+  </si>
+  <si>
+    <t>coatings\Asahi\CSD_model_45deg_transmission.csv</t>
+  </si>
+  <si>
+    <t>this is the old one what we designed to</t>
+  </si>
+  <si>
+    <t>Keck Blue Book (page 4-8), for reference for telescope area calculation</t>
+  </si>
+  <si>
+    <t>Emissivity</t>
+  </si>
+  <si>
+    <t>1-T</t>
+  </si>
+  <si>
+    <t>1-R</t>
+  </si>
+  <si>
+    <t>ATC Doublet - N-SF6</t>
+  </si>
+  <si>
+    <t>ATC Doublet - N-LAK22</t>
+  </si>
+  <si>
+    <t>ATC lens - BSL7Y</t>
+  </si>
+  <si>
+    <t>ATC lens - Cleartran</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>273</t>
   </si>
 </sst>
 </file>
@@ -775,7 +799,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,12 +862,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -876,6 +894,24 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -935,7 +971,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -981,15 +1017,22 @@
     <xf numFmtId="2" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2162,10 +2205,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F112" dT="2024-08-08T00:13:48.98" personId="{A1FA452A-7AE5-5E47-BFE8-E116E5BB88FD}" id="{56141629-55F1-1446-BFB4-120BC87945C5}">
+  <threadedComment ref="H113" dT="2024-08-08T00:13:48.98" personId="{A1FA452A-7AE5-5E47-BFE8-E116E5BB88FD}" id="{56141629-55F1-1446-BFB4-120BC87945C5}">
     <text>Update this to LGS option</text>
   </threadedComment>
-  <threadedComment ref="C119" dT="2024-08-08T01:28:37.98" personId="{A1FA452A-7AE5-5E47-BFE8-E116E5BB88FD}" id="{7F1D9F1A-5EC9-6C43-BCC4-B706F903AA15}">
+  <threadedComment ref="C120" dT="2024-08-08T01:28:37.98" personId="{A1FA452A-7AE5-5E47-BFE8-E116E5BB88FD}" id="{7F1D9F1A-5EC9-6C43-BCC4-B706F903AA15}">
     <text>Need to add this as an option</text>
   </threadedComment>
 </ThreadedComments>
@@ -2173,22 +2216,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:L155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="86.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="122" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="2"/>
+    <col min="5" max="5" width="12.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="86.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="122" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2202,22 +2247,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="b">
         <v>0</v>
       </c>
@@ -2233,8 +2284,10 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>1</v>
       </c>
@@ -2247,19 +2300,25 @@
       <c r="D3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="29"/>
+      <c r="E3" s="28" t="s">
+        <v>221</v>
+      </c>
       <c r="F3" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="I3" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="J3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="28"/>
-    </row>
-    <row r="4" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="28"/>
+    </row>
+    <row r="4" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27">
         <v>1</v>
       </c>
@@ -2272,19 +2331,25 @@
       <c r="D4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="28" t="s">
+        <v>221</v>
+      </c>
       <c r="F4" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="I4" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="J4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="28"/>
-    </row>
-    <row r="5" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="28"/>
+    </row>
+    <row r="5" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27">
         <v>1</v>
       </c>
@@ -2297,17 +2362,23 @@
       <c r="D5" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="28" t="s">
+        <v>221</v>
+      </c>
       <c r="F5" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="I5" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-    </row>
-    <row r="6" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+    </row>
+    <row r="6" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="27">
         <v>1</v>
       </c>
@@ -2320,17 +2391,19 @@
       <c r="D6" s="27">
         <v>0.99299999999999999</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="28" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="J6" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="28"/>
-    </row>
-    <row r="7" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="28"/>
+    </row>
+    <row r="7" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="27">
         <v>0</v>
       </c>
@@ -2343,19 +2416,21 @@
       <c r="D7" s="27">
         <v>0.95499999999999996</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="28" t="s">
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="28"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="K7" s="28"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="b">
         <v>0</v>
       </c>
@@ -2363,16 +2438,18 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27">
         <v>1</v>
       </c>
@@ -2380,20 +2457,26 @@
         <v>11</v>
       </c>
       <c r="C9" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="29"/>
+      <c r="H9" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
       <c r="I9" s="28"/>
-    </row>
-    <row r="10" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+    </row>
+    <row r="10" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27">
         <v>1</v>
       </c>
@@ -2401,20 +2484,26 @@
         <v>21</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="56" t="s">
+        <v>221</v>
+      </c>
       <c r="F10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+        <v>227</v>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I10" s="28"/>
-    </row>
-    <row r="11" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+    </row>
+    <row r="11" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27">
         <v>1</v>
       </c>
@@ -2422,20 +2511,26 @@
         <v>11</v>
       </c>
       <c r="C11" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
       <c r="I11" s="28"/>
-    </row>
-    <row r="12" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+    </row>
+    <row r="12" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27">
         <v>1</v>
       </c>
@@ -2443,20 +2538,26 @@
         <v>21</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="56" t="s">
+        <v>221</v>
+      </c>
       <c r="F12" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+        <v>227</v>
+      </c>
+      <c r="G12" s="29"/>
+      <c r="H12" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I12" s="28"/>
-    </row>
-    <row r="13" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+    </row>
+    <row r="13" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="27">
         <v>1</v>
       </c>
@@ -2464,20 +2565,26 @@
         <v>11</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="29"/>
+      <c r="E13" s="31" t="s">
+        <v>221</v>
+      </c>
       <c r="F13" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
+        <v>227</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="I13" s="28"/>
-    </row>
-    <row r="14" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+    </row>
+    <row r="14" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="27">
         <v>1</v>
       </c>
@@ -2485,20 +2592,26 @@
         <v>21</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E14" s="29"/>
+      <c r="E14" s="56" t="s">
+        <v>221</v>
+      </c>
       <c r="F14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+        <v>227</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I14" s="28"/>
-    </row>
-    <row r="15" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+    </row>
+    <row r="15" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27">
         <v>1</v>
       </c>
@@ -2506,20 +2619,26 @@
         <v>11</v>
       </c>
       <c r="C15" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
       <c r="I15" s="28"/>
-    </row>
-    <row r="16" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+    </row>
+    <row r="16" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27">
         <v>1</v>
       </c>
@@ -2527,20 +2646,26 @@
         <v>21</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E16" s="29"/>
-      <c r="F16" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="E16" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F16" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I16" s="28"/>
-    </row>
-    <row r="17" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+    </row>
+    <row r="17" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="27">
         <v>1</v>
       </c>
@@ -2548,20 +2673,26 @@
         <v>11</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="E17" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="28" t="s">
+        <v>34</v>
+      </c>
       <c r="I17" s="28"/>
-    </row>
-    <row r="18" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+    </row>
+    <row r="18" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>1</v>
       </c>
@@ -2569,20 +2700,26 @@
         <v>21</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
+      <c r="E18" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I18" s="28"/>
-    </row>
-    <row r="19" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+    </row>
+    <row r="19" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27">
         <v>1</v>
       </c>
@@ -2590,20 +2727,26 @@
         <v>11</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
+      <c r="E19" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F19" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G19" s="29"/>
+      <c r="H19" s="28" t="s">
+        <v>31</v>
+      </c>
       <c r="I19" s="28"/>
-    </row>
-    <row r="20" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+    </row>
+    <row r="20" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="27">
         <v>1</v>
       </c>
@@ -2611,20 +2754,26 @@
         <v>21</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E20" s="29"/>
-      <c r="F20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
+      <c r="E20" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F20" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G20" s="29"/>
+      <c r="H20" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I20" s="28"/>
-    </row>
-    <row r="21" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+    </row>
+    <row r="21" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27">
         <v>1</v>
       </c>
@@ -2632,20 +2781,26 @@
         <v>11</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
+      <c r="E21" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F21" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="28" t="s">
+        <v>34</v>
+      </c>
       <c r="I21" s="28"/>
-    </row>
-    <row r="22" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+    </row>
+    <row r="22" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="27">
         <v>1</v>
       </c>
@@ -2653,20 +2808,26 @@
         <v>21</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="E22" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F22" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="29"/>
+      <c r="H22" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I22" s="28"/>
-    </row>
-    <row r="23" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+    </row>
+    <row r="23" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27">
         <v>1</v>
       </c>
@@ -2674,20 +2835,26 @@
         <v>11</v>
       </c>
       <c r="C23" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="56">
+        <v>0.02</v>
+      </c>
+      <c r="F23" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G23" s="29"/>
+      <c r="H23" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
       <c r="I23" s="28"/>
-    </row>
-    <row r="24" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+    </row>
+    <row r="24" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27">
         <v>1</v>
       </c>
@@ -2695,20 +2862,26 @@
         <v>21</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E24" s="29"/>
-      <c r="F24" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="E24" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G24" s="29"/>
+      <c r="H24" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I24" s="28"/>
-    </row>
-    <row r="25" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+    </row>
+    <row r="25" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="27">
         <v>1</v>
       </c>
@@ -2716,20 +2889,26 @@
         <v>11</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
+      <c r="E25" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G25" s="29"/>
+      <c r="H25" s="28" t="s">
+        <v>28</v>
+      </c>
       <c r="I25" s="28"/>
-    </row>
-    <row r="26" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+    </row>
+    <row r="26" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="27">
         <v>1</v>
       </c>
@@ -2737,20 +2916,26 @@
         <v>21</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="27">
         <v>0.97799999999999998</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="E26" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F26" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="I26" s="28"/>
-    </row>
-    <row r="27" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+    </row>
+    <row r="27" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27">
         <v>1</v>
       </c>
@@ -2758,43 +2943,51 @@
         <v>21</v>
       </c>
       <c r="C27" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="31">
+        <v>1</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="31">
-        <v>1</v>
-      </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29" t="s">
+      <c r="K27" s="29"/>
+    </row>
+    <row r="28" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <v>1</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="I27" s="29"/>
-    </row>
-    <row r="28" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27">
-        <v>1</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="28" t="s">
+      <c r="D28" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29" t="s">
+      <c r="I28" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="b">
         <v>0</v>
       </c>
@@ -2802,86 +2995,98 @@
         <v>9</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <v>1</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
-        <v>1</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="28" t="s">
+      <c r="D30" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29" t="s">
+      <c r="I30" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="J30" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="H30" s="29" t="s">
+      <c r="K30" s="29"/>
+    </row>
+    <row r="31" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <v>1</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="I30" s="29"/>
-    </row>
-    <row r="31" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
-        <v>1</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>52</v>
-      </c>
       <c r="D31" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29" t="s">
-        <v>53</v>
-      </c>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="K31" s="29"/>
+    </row>
+    <row r="32" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <v>1</v>
+      </c>
+      <c r="B32" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="I31" s="29"/>
-    </row>
-    <row r="32" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27">
-        <v>1</v>
-      </c>
-      <c r="B32" s="28" t="s">
+      <c r="C32" s="28" t="s">
         <v>55</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>56</v>
       </c>
       <c r="D32" s="31">
         <v>4</v>
       </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29" t="s">
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="27">
         <v>1</v>
       </c>
@@ -2889,64 +3094,70 @@
         <v>11</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29" t="s">
-        <v>53</v>
-      </c>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
       <c r="G33" s="29"/>
       <c r="H33" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33" s="29"/>
+    </row>
+    <row r="34" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="39">
+        <v>1</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="29"/>
-    </row>
-    <row r="34" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="39">
-        <v>1</v>
-      </c>
-      <c r="B34" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="40" t="s">
+      <c r="D34" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41" t="s">
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+    </row>
+    <row r="35" spans="1:11" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <v>1</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="28" t="s">
         <v>61</v>
-      </c>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-    </row>
-    <row r="35" spans="1:9" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27">
-        <v>1</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>62</v>
       </c>
       <c r="D35" s="31">
         <v>4</v>
       </c>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29" t="s">
-        <v>63</v>
-      </c>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
+      <c r="H35" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="I35" s="29"/>
-    </row>
-    <row r="36" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+    </row>
+    <row r="36" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>1</v>
       </c>
@@ -2954,20 +3165,22 @@
         <v>11</v>
       </c>
       <c r="C36" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D36" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
       <c r="I36" s="41"/>
-    </row>
-    <row r="37" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J36" s="41"/>
+      <c r="K36" s="41"/>
+    </row>
+    <row r="37" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="27">
         <v>1</v>
       </c>
@@ -2975,43 +3188,47 @@
         <v>11</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29" t="s">
-        <v>53</v>
-      </c>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
       <c r="G37" s="29"/>
       <c r="H37" s="29" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I37" s="29"/>
-    </row>
-    <row r="38" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J37" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="K37" s="29"/>
+    </row>
+    <row r="38" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27">
         <v>1</v>
       </c>
       <c r="B38" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>55</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>56</v>
       </c>
       <c r="D38" s="31">
         <v>4</v>
       </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29" t="s">
-        <v>57</v>
-      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
       <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
+      <c r="H38" s="29" t="s">
+        <v>56</v>
+      </c>
       <c r="I38" s="29"/>
-    </row>
-    <row r="39" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+    </row>
+    <row r="39" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="27">
         <v>1</v>
       </c>
@@ -3019,20 +3236,22 @@
         <v>11</v>
       </c>
       <c r="C39" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
       <c r="I39" s="29"/>
-    </row>
-    <row r="40" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+    </row>
+    <row r="40" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>1</v>
       </c>
@@ -3040,41 +3259,45 @@
         <v>11</v>
       </c>
       <c r="C40" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41" t="s">
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="41"/>
+    </row>
+    <row r="41" spans="1:11" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="27">
+        <v>1</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>61</v>
-      </c>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
-    </row>
-    <row r="41" spans="1:9" s="30" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="27">
-        <v>1</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>62</v>
       </c>
       <c r="D41" s="31">
         <v>4</v>
       </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29" t="s">
-        <v>63</v>
-      </c>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
       <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
+      <c r="H41" s="29" t="s">
+        <v>62</v>
+      </c>
       <c r="I41" s="29"/>
-    </row>
-    <row r="42" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+    </row>
+    <row r="42" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>1</v>
       </c>
@@ -3082,20 +3305,22 @@
         <v>11</v>
       </c>
       <c r="C42" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
       <c r="I42" s="41"/>
-    </row>
-    <row r="43" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J42" s="41"/>
+      <c r="K42" s="41"/>
+    </row>
+    <row r="43" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="27">
         <v>1</v>
       </c>
@@ -3103,22 +3328,28 @@
         <v>11</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D43" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29" t="s">
+      <c r="E43" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="F43" s="60" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="G43" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="b">
         <v>0</v>
       </c>
@@ -3126,100 +3357,126 @@
         <v>9</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D44" s="14"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+    </row>
+    <row r="45" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>2</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="49" t="s">
+      <c r="C45" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="F45" s="59">
+        <v>273</v>
+      </c>
+      <c r="G45" s="17"/>
+      <c r="H45" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="D45" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="17"/>
-      <c r="F45" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
       <c r="I45" s="16"/>
-    </row>
-    <row r="46" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+    </row>
+    <row r="46" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>3</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="F46" s="59">
+        <v>273</v>
+      </c>
+      <c r="G46" s="17"/>
+      <c r="H46" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="17"/>
-      <c r="F46" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
       <c r="I46" s="16"/>
-    </row>
-    <row r="47" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+    </row>
+    <row r="47" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>4</v>
       </c>
       <c r="B47" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="49" t="s">
+      <c r="C47" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="F47" s="59">
+        <v>273</v>
+      </c>
+      <c r="G47" s="17"/>
+      <c r="H47" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D47" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="17"/>
-      <c r="F47" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
       <c r="I47" s="16"/>
-    </row>
-    <row r="48" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+    </row>
+    <row r="48" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
         <v>5</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="49" t="s">
+      <c r="C48" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="F48" s="59">
+        <v>273</v>
+      </c>
+      <c r="G48" s="17"/>
+      <c r="H48" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D48" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
       <c r="I48" s="16"/>
-    </row>
-    <row r="49" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+    </row>
+    <row r="49" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>1</v>
       </c>
@@ -3227,20 +3484,22 @@
         <v>21</v>
       </c>
       <c r="C49" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D49" s="15">
+        <v>1</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="15">
-        <v>1</v>
-      </c>
-      <c r="E49" s="17"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I49" s="16"/>
-    </row>
-    <row r="50" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K49" s="16"/>
+    </row>
+    <row r="50" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>1</v>
       </c>
@@ -3248,77 +3507,83 @@
         <v>21</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D50" s="15">
         <v>0.99</v>
       </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="16" t="s">
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I50" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G50" s="16" t="s">
+      <c r="J50" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="H50" s="16" t="s">
+      <c r="K50" s="16"/>
+      <c r="L50" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="I50" s="16"/>
-      <c r="J50" s="47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
         <v>1</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>82</v>
+        <v>223</v>
       </c>
       <c r="D51" s="15">
         <v>14.5</v>
       </c>
-      <c r="E51" s="17"/>
-      <c r="F51" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H51" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I51" s="16"/>
-    </row>
-    <row r="52" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="K51" s="16"/>
+    </row>
+    <row r="52" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>1</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="D52" s="15">
         <v>5.5</v>
       </c>
-      <c r="E52" s="17"/>
-      <c r="F52" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="17"/>
       <c r="H52" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="I52" s="16"/>
-    </row>
-    <row r="53" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="K52" s="16"/>
+    </row>
+    <row r="53" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15">
         <v>1</v>
       </c>
@@ -3326,22 +3591,24 @@
         <v>21</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D53" s="15">
         <v>0.99</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="16" t="s">
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I53" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G53" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-    </row>
-    <row r="54" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+    </row>
+    <row r="54" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="15">
         <v>1</v>
       </c>
@@ -3349,72 +3616,78 @@
         <v>21</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D54" s="15">
         <v>0.99</v>
       </c>
-      <c r="E54" s="17"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I54" s="16"/>
-    </row>
-    <row r="55" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" s="16"/>
+    </row>
+    <row r="55" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15">
         <v>1</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="D55" s="15">
         <v>14.3</v>
       </c>
-      <c r="E55" s="17"/>
-      <c r="F55" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="17"/>
       <c r="H55" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I55" s="16"/>
-    </row>
-    <row r="56" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="K55" s="16"/>
+    </row>
+    <row r="56" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15">
         <v>1</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="D56" s="15">
         <v>4.3</v>
       </c>
-      <c r="E56" s="17"/>
-      <c r="F56" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>96</v>
-      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="17"/>
       <c r="H56" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I56" s="16"/>
-    </row>
-    <row r="57" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="I56" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="K56" s="16"/>
+    </row>
+    <row r="57" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15">
         <v>1</v>
       </c>
@@ -3422,72 +3695,86 @@
         <v>21</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D57" s="15">
         <v>0.99</v>
       </c>
-      <c r="E57" s="17"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="H57" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="I57" s="16"/>
-    </row>
-    <row r="58" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="J57" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="K57" s="16"/>
+    </row>
+    <row r="58" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15">
         <v>1</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="45" t="s">
+      <c r="C58" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F58" s="15">
+        <v>273</v>
+      </c>
+      <c r="G58" s="17"/>
+      <c r="H58" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J58" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="K58" s="43"/>
+    </row>
+    <row r="59" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
+        <v>1</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="15">
+        <v>0.02</v>
+      </c>
+      <c r="F59" s="15">
+        <v>80</v>
+      </c>
+      <c r="G59" s="17"/>
+      <c r="H59" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D58" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="17"/>
-      <c r="F58" s="18" t="s">
+      <c r="I59" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="J59" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="H58" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="I58" s="45"/>
-    </row>
-    <row r="59" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15">
-        <v>1</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="17"/>
-      <c r="F59" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I59" s="16"/>
-    </row>
-    <row r="60" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K59" s="16"/>
+    </row>
+    <row r="60" spans="1:12" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>1</v>
       </c>
@@ -3495,22 +3782,24 @@
         <v>21</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D60" s="36">
         <v>0.82</v>
       </c>
-      <c r="E60" s="17"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="H60" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I60" s="16"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="J60" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="K60" s="16"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="b">
         <v>0</v>
       </c>
@@ -3518,7 +3807,7 @@
         <v>9</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -3526,102 +3815,128 @@
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>2</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="48" t="s">
-        <v>67</v>
+      <c r="C62" s="46" t="s">
+        <v>66</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="11"/>
-      <c r="F62" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="G62" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I62" s="10"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E62" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F62" s="7">
+        <v>273</v>
+      </c>
+      <c r="G62" s="11"/>
+      <c r="H62" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J62" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K62" s="10"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>3</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C63" s="48" t="s">
-        <v>69</v>
+      <c r="C63" s="46" t="s">
+        <v>68</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="11"/>
-      <c r="F63" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E63" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F63" s="7">
+        <v>273</v>
+      </c>
+      <c r="G63" s="11"/>
+      <c r="H63" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>4</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="48" t="s">
-        <v>71</v>
+      <c r="C64" s="46" t="s">
+        <v>70</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E64" s="11"/>
-      <c r="F64" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E64" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F64" s="7">
+        <v>273</v>
+      </c>
+      <c r="G64" s="11"/>
+      <c r="H64" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>5</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="48" t="s">
-        <v>73</v>
+      <c r="C65" s="46" t="s">
+        <v>72</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E65" s="11"/>
-      <c r="F65" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E65" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F65" s="7">
+        <v>273</v>
+      </c>
+      <c r="G65" s="11"/>
+      <c r="H65" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>1</v>
       </c>
@@ -3629,47 +3944,61 @@
         <v>11</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="9">
-        <v>1</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="11"/>
-      <c r="F67" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I67" s="11"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E66" s="58">
+        <v>0.02</v>
+      </c>
+      <c r="F66" s="7">
+        <v>273</v>
+      </c>
+      <c r="G66" s="11"/>
+      <c r="H66" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K66" s="11"/>
+    </row>
+    <row r="67" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="52">
+        <v>0</v>
+      </c>
+      <c r="B67" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="52">
+        <v>0.02</v>
+      </c>
+      <c r="F67" s="52">
+        <v>273</v>
+      </c>
+      <c r="G67" s="54"/>
+      <c r="H67" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="I67" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J67" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="K67" s="54"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1</v>
       </c>
@@ -3677,108 +4006,118 @@
         <v>21</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D68" s="7">
         <v>0.998</v>
       </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="8"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
       <c r="G68" s="11"/>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="8"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="K68" s="10"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="9">
+        <v>1</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K69" s="11"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="9">
+        <v>1</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="K70" s="11"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="9">
+        <v>1</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="I68" s="10"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="9">
-        <v>1</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="10" t="s">
+      <c r="D71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+    </row>
+    <row r="72" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="9">
+        <v>1</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D69" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="11"/>
-      <c r="F69" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="I69" s="11"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="9">
-        <v>1</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="11"/>
-      <c r="F70" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="I70" s="11"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="9">
-        <v>1</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-    </row>
-    <row r="72" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="9">
-        <v>1</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>128</v>
-      </c>
       <c r="D72" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="11"/>
-      <c r="F72" s="8" t="s">
-        <v>123</v>
-      </c>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
       <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
+      <c r="H72" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="I72" s="11"/>
-    </row>
-    <row r="73" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+    </row>
+    <row r="73" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>1</v>
       </c>
@@ -3786,42 +4125,46 @@
         <v>21</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D73" s="7">
         <f>1-0.0035</f>
         <v>0.99650000000000005</v>
       </c>
-      <c r="E73" s="11"/>
-      <c r="F73" s="8"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
       <c r="G73" s="11"/>
-      <c r="H73" s="11" t="s">
-        <v>130</v>
-      </c>
+      <c r="H73" s="8"/>
       <c r="I73" s="11"/>
-    </row>
-    <row r="74" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J73" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="K73" s="11"/>
+    </row>
+    <row r="74" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>1</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D74" s="7">
         <v>10</v>
       </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="26" t="s">
-        <v>132</v>
-      </c>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
       <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
+      <c r="H74" s="26" t="s">
+        <v>126</v>
+      </c>
       <c r="I74" s="11"/>
-    </row>
-    <row r="75" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+    </row>
+    <row r="75" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>1</v>
       </c>
@@ -3829,19 +4172,21 @@
         <v>21</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D75" s="7">
         <f>1-0.005</f>
         <v>0.995</v>
       </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="26"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
       <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
+      <c r="H75" s="26"/>
       <c r="I75" s="11"/>
-    </row>
-    <row r="76" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+    </row>
+    <row r="76" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>1</v>
       </c>
@@ -3849,40 +4194,44 @@
         <v>21</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D76" s="7">
         <f>1-0.005</f>
         <v>0.995</v>
       </c>
-      <c r="E76" s="11"/>
-      <c r="F76" s="26"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
       <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
+      <c r="H76" s="26"/>
       <c r="I76" s="11"/>
-    </row>
-    <row r="77" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+    </row>
+    <row r="77" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>1</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D77" s="7">
         <v>2.73</v>
       </c>
-      <c r="E77" s="11"/>
-      <c r="F77" s="26" t="s">
-        <v>135</v>
-      </c>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
       <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
+      <c r="H77" s="26" t="s">
+        <v>129</v>
+      </c>
       <c r="I77" s="11"/>
-    </row>
-    <row r="78" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+    </row>
+    <row r="78" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>1</v>
       </c>
@@ -3890,19 +4239,21 @@
         <v>21</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D78" s="7">
         <f>1-0.0035</f>
         <v>0.99650000000000005</v>
       </c>
-      <c r="E78" s="11"/>
-      <c r="F78" s="26"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
       <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
+      <c r="H78" s="26"/>
       <c r="I78" s="11"/>
-    </row>
-    <row r="79" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+    </row>
+    <row r="79" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>1</v>
       </c>
@@ -3910,40 +4261,44 @@
         <v>21</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D79" s="7">
         <f>1-0.0035</f>
         <v>0.99650000000000005</v>
       </c>
-      <c r="E79" s="11"/>
-      <c r="F79" s="26"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
       <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
+      <c r="H79" s="26"/>
       <c r="I79" s="11"/>
-    </row>
-    <row r="80" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+    </row>
+    <row r="80" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>1</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D80" s="25">
         <v>10</v>
       </c>
-      <c r="E80" s="11"/>
-      <c r="F80" s="26" t="s">
-        <v>137</v>
-      </c>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
       <c r="G80" s="11"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-    </row>
-    <row r="81" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H80" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="I80" s="11"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="10"/>
+    </row>
+    <row r="81" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>1</v>
       </c>
@@ -3951,19 +4306,21 @@
         <v>21</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D81" s="25">
         <f>1-0.0035</f>
         <v>0.99650000000000005</v>
       </c>
-      <c r="E81" s="11"/>
-      <c r="F81" s="26"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
       <c r="G81" s="11"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H81" s="26"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="b">
         <v>0</v>
       </c>
@@ -3971,7 +4328,7 @@
         <v>9</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -3979,351 +4336,412 @@
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
-    </row>
-    <row r="83" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+    </row>
+    <row r="83" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="19">
         <v>2</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C83" s="51" t="s">
-        <v>67</v>
+      <c r="C83" s="49" t="s">
+        <v>66</v>
       </c>
       <c r="D83" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E83" s="21"/>
-      <c r="F83" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="G83" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-    </row>
-    <row r="84" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E83" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="F83" s="19">
+        <v>273</v>
+      </c>
+      <c r="G83" s="21"/>
+      <c r="H83" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="I83" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20"/>
+    </row>
+    <row r="84" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="19">
         <v>3</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C84" s="51" t="s">
-        <v>69</v>
+      <c r="C84" s="49" t="s">
+        <v>68</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="G84" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-    </row>
-    <row r="85" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E84" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="F84" s="19">
+        <v>273</v>
+      </c>
+      <c r="G84" s="21"/>
+      <c r="H84" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="I84" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J84" s="20"/>
+      <c r="K84" s="20"/>
+    </row>
+    <row r="85" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="19">
         <v>4</v>
       </c>
       <c r="B85" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C85" s="51" t="s">
-        <v>71</v>
+      <c r="C85" s="49" t="s">
+        <v>70</v>
       </c>
       <c r="D85" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E85" s="21"/>
-      <c r="F85" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="G85" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-    </row>
-    <row r="86" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E85" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="F85" s="19">
+        <v>273</v>
+      </c>
+      <c r="G85" s="21"/>
+      <c r="H85" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="I85" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J85" s="20"/>
+      <c r="K85" s="20"/>
+    </row>
+    <row r="86" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="19">
         <v>5</v>
       </c>
       <c r="B86" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C86" s="51" t="s">
-        <v>73</v>
+      <c r="C86" s="49" t="s">
+        <v>72</v>
       </c>
       <c r="D86" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E86" s="21"/>
-      <c r="F86" s="53" t="s">
+      <c r="E86" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="F86" s="19">
+        <v>273</v>
+      </c>
+      <c r="G86" s="21"/>
+      <c r="H86" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="I86" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
+    </row>
+    <row r="87" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="19">
+        <v>1</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="19"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="I87" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J87" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="K87" s="20"/>
+    </row>
+    <row r="88" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="19">
+        <v>1</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="F88" s="19">
+        <v>273</v>
+      </c>
+      <c r="G88" s="21"/>
+      <c r="H88" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="I88" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J88" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="K88" s="20"/>
+    </row>
+    <row r="89" spans="1:11" s="55" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="52">
+        <v>0</v>
+      </c>
+      <c r="B89" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D89" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="52">
+        <v>0.02</v>
+      </c>
+      <c r="F89" s="52">
+        <v>273</v>
+      </c>
+      <c r="G89" s="54"/>
+      <c r="H89" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="I89" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="J89" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="K89" s="53"/>
+    </row>
+    <row r="90" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="19">
+        <v>1</v>
+      </c>
+      <c r="B90" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="19"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="I90" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="J90" s="20"/>
+      <c r="K90" s="20"/>
+    </row>
+    <row r="91" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="19">
+        <v>1</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G86" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-    </row>
-    <row r="87" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="19">
-        <v>1</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D87" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="20" t="s">
+      <c r="D91" s="19">
+        <v>0.998</v>
+      </c>
+      <c r="E91" s="19"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="21"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="K91" s="20"/>
+    </row>
+    <row r="92" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="19">
+        <v>1</v>
+      </c>
+      <c r="B92" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="G87" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H87" s="20" t="s">
+      <c r="D92" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="19"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="21"/>
+      <c r="H92" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="I87" s="20"/>
-    </row>
-    <row r="88" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="19">
-        <v>1</v>
-      </c>
-      <c r="B88" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="20" t="s">
+      <c r="I92" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D88" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="21"/>
-      <c r="F88" s="20" t="s">
+      <c r="J92" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G88" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H88" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="I88" s="20"/>
-    </row>
-    <row r="89" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="19">
-        <v>1</v>
-      </c>
-      <c r="B89" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C89" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="21"/>
-      <c r="F89" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="G89" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H89" s="20"/>
-      <c r="I89" s="20"/>
-    </row>
-    <row r="90" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="19">
-        <v>1</v>
-      </c>
-      <c r="B90" s="20" t="s">
+      <c r="K92" s="21"/>
+    </row>
+    <row r="93" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="19">
+        <v>1</v>
+      </c>
+      <c r="B93" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D93" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="19"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="21"/>
+      <c r="H93" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="I93" s="20"/>
+      <c r="J93" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="K93" s="21"/>
+    </row>
+    <row r="94" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="19">
+        <v>1</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="19"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="I94" s="20"/>
+      <c r="J94" s="21"/>
+      <c r="K94" s="21"/>
+    </row>
+    <row r="95" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="19">
+        <v>1</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="19"/>
+      <c r="F95" s="19"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="I95" s="20"/>
+      <c r="J95" s="21"/>
+      <c r="K95" s="21"/>
+    </row>
+    <row r="96" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="19">
+        <v>1</v>
+      </c>
+      <c r="B96" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C90" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="D90" s="19">
-        <v>0.998</v>
-      </c>
-      <c r="E90" s="21"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="I90" s="20"/>
-    </row>
-    <row r="91" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="19">
-        <v>1</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D91" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="21"/>
-      <c r="F91" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="G91" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="H91" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="I91" s="21"/>
-    </row>
-    <row r="92" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="19">
-        <v>1</v>
-      </c>
-      <c r="B92" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C92" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D92" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="21"/>
-      <c r="F92" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="G92" s="20"/>
-      <c r="H92" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="I92" s="21"/>
-    </row>
-    <row r="93" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="19">
-        <v>1</v>
-      </c>
-      <c r="B93" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D93" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="21"/>
-      <c r="F93" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="G93" s="20"/>
-      <c r="H93" s="21"/>
-      <c r="I93" s="21"/>
-    </row>
-    <row r="94" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="19">
-        <v>1</v>
-      </c>
-      <c r="B94" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C94" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="21"/>
-      <c r="F94" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="G94" s="20"/>
-      <c r="H94" s="21"/>
-      <c r="I94" s="21"/>
-    </row>
-    <row r="95" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="19">
-        <v>1</v>
-      </c>
-      <c r="B95" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D95" s="19">
+      <c r="C96" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D96" s="19">
         <f>1-0.007</f>
         <v>0.99299999999999999</v>
       </c>
-      <c r="E95" s="21"/>
-      <c r="F95" s="20"/>
-      <c r="G95" s="21"/>
-      <c r="H95" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="I95" s="21"/>
-    </row>
-    <row r="96" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="19">
-        <v>1</v>
-      </c>
-      <c r="B96" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D96" s="19">
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="21"/>
+      <c r="J96" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="K96" s="21"/>
+    </row>
+    <row r="97" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="19">
+        <v>1</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D97" s="19">
         <v>10</v>
       </c>
-      <c r="E96" s="21"/>
-      <c r="F96" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="G96" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="H96" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="I96" s="21"/>
-    </row>
-    <row r="97" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="19">
-        <v>1</v>
-      </c>
-      <c r="B97" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="D97" s="19">
-        <f>1-0.007</f>
-        <v>0.99299999999999999</v>
-      </c>
-      <c r="E97" s="21"/>
-      <c r="F97" s="20"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
       <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="21"/>
-    </row>
-    <row r="98" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H97" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="I97" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J97" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="K97" s="21"/>
+    </row>
+    <row r="98" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="19">
         <v>1</v>
       </c>
@@ -4331,62 +4749,68 @@
         <v>21</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D98" s="19">
         <f>1-0.007</f>
         <v>0.99299999999999999</v>
       </c>
-      <c r="E98" s="21"/>
-      <c r="F98" s="20"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
       <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
+      <c r="H98" s="20"/>
       <c r="I98" s="21"/>
-    </row>
-    <row r="99" spans="1:9" s="22" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J98" s="21"/>
+      <c r="K98" s="21"/>
+    </row>
+    <row r="99" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="19">
         <v>1</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="D99" s="19">
-        <v>4</v>
-      </c>
-      <c r="E99" s="21"/>
-      <c r="F99" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G99" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="H99" s="21"/>
-      <c r="I99" s="21"/>
-    </row>
-    <row r="100" spans="1:9" s="22" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="19">
-        <v>1</v>
-      </c>
-      <c r="B100" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="D100" s="19">
         <f>1-0.007</f>
         <v>0.99299999999999999</v>
       </c>
-      <c r="E100" s="21"/>
-      <c r="F100" s="20"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="19"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
+      <c r="K99" s="21"/>
+    </row>
+    <row r="100" spans="1:11" s="22" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="19">
+        <v>1</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D100" s="19">
+        <v>4</v>
+      </c>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19"/>
       <c r="G100" s="21"/>
-      <c r="H100" s="21"/>
-      <c r="I100" s="21"/>
-    </row>
-    <row r="101" spans="1:9" s="22" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H100" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I100" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J100" s="21"/>
+      <c r="K100" s="21"/>
+    </row>
+    <row r="101" spans="1:11" s="22" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="19">
         <v>1</v>
       </c>
@@ -4394,230 +4818,247 @@
         <v>21</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D101" s="19">
         <f>1-0.007</f>
         <v>0.99299999999999999</v>
       </c>
-      <c r="E101" s="21"/>
-      <c r="F101" s="20"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="19"/>
       <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
+      <c r="H101" s="20"/>
       <c r="I101" s="21"/>
-    </row>
-    <row r="102" spans="1:9" s="22" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+    </row>
+    <row r="102" spans="1:11" s="22" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="19">
         <v>1</v>
       </c>
       <c r="B102" s="20" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C102" s="20" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D102" s="19">
-        <v>10</v>
-      </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G102" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
-    </row>
-    <row r="103" spans="1:9" s="22" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="19">
-        <v>1</v>
-      </c>
-      <c r="B103" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="D103" s="19">
         <f>1-0.007</f>
         <v>0.99299999999999999</v>
       </c>
-      <c r="E103" s="21"/>
-      <c r="F103" s="20"/>
+      <c r="E102" s="19"/>
+      <c r="F102" s="19"/>
+      <c r="G102" s="21"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="21"/>
+      <c r="J102" s="21"/>
+      <c r="K102" s="21"/>
+    </row>
+    <row r="103" spans="1:11" s="22" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="19">
+        <v>1</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="D103" s="19">
+        <v>10</v>
+      </c>
+      <c r="E103" s="19"/>
+      <c r="F103" s="19"/>
       <c r="G103" s="21"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="b">
+      <c r="H103" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="I103" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J103" s="20"/>
+      <c r="K103" s="20"/>
+    </row>
+    <row r="104" spans="1:11" s="22" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="19">
+        <v>1</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D104" s="19">
+        <f>1-0.007</f>
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="E104" s="19"/>
+      <c r="F104" s="19"/>
+      <c r="G104" s="21"/>
+      <c r="H104" s="20"/>
+      <c r="I104" s="21"/>
+      <c r="J104" s="20"/>
+      <c r="K104" s="20"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B105" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C105" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+    </row>
+    <row r="106" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="27">
+        <v>1</v>
+      </c>
+      <c r="B106" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D106" s="33">
+        <v>1.3</v>
+      </c>
+      <c r="E106" s="33"/>
+      <c r="F106" s="33"/>
+      <c r="G106" s="33"/>
+      <c r="H106" s="33"/>
+      <c r="I106" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="J106" s="29"/>
+      <c r="K106" s="29"/>
+    </row>
+    <row r="107" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="27">
+        <v>1</v>
+      </c>
+      <c r="B107" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D107" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="33"/>
+      <c r="F107" s="33"/>
+      <c r="G107" s="33"/>
+      <c r="H107" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="I107" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="J107" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="K107" s="29"/>
+    </row>
+    <row r="108" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="27">
+        <v>1</v>
+      </c>
+      <c r="B108" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-    </row>
-    <row r="105" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="27">
-        <v>1</v>
-      </c>
-      <c r="B105" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C105" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="D105" s="33">
-        <v>1.3</v>
-      </c>
-      <c r="E105" s="33"/>
-      <c r="F105" s="33"/>
-      <c r="G105" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="H105" s="29"/>
-      <c r="I105" s="29"/>
-    </row>
-    <row r="106" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="27">
-        <v>1</v>
-      </c>
-      <c r="B106" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C106" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="D106" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="33"/>
-      <c r="F106" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="G106" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="H106" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="I106" s="29"/>
-    </row>
-    <row r="107" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="27">
-        <v>1</v>
-      </c>
-      <c r="B107" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C107" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="D107" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="33"/>
-      <c r="F107" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="G107" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="H107" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="I107" s="29"/>
-    </row>
-    <row r="108" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="27">
-        <v>1</v>
-      </c>
-      <c r="B108" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C108" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D108" s="33">
-        <v>0.99</v>
+      <c r="D108" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="E108" s="33"/>
       <c r="F108" s="33"/>
-      <c r="G108" s="29"/>
-      <c r="H108" s="29"/>
-      <c r="I108" s="29"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="b">
+      <c r="G108" s="33"/>
+      <c r="H108" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="I108" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="J108" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="K108" s="29"/>
+    </row>
+    <row r="109" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="27">
+        <v>1</v>
+      </c>
+      <c r="B109" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D109" s="33">
+        <v>0.99</v>
+      </c>
+      <c r="E109" s="33"/>
+      <c r="F109" s="33"/>
+      <c r="G109" s="33"/>
+      <c r="H109" s="33"/>
+      <c r="I109" s="29"/>
+      <c r="J109" s="29"/>
+      <c r="K109" s="29"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B110" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-    </row>
-    <row r="110" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="27">
-        <v>1</v>
-      </c>
-      <c r="B110" s="32" t="s">
+      <c r="C110" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+    </row>
+    <row r="111" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="27">
+        <v>1</v>
+      </c>
+      <c r="B111" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C110" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="D110" s="33">
+      <c r="C111" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D111" s="33">
         <v>1.3</v>
       </c>
-      <c r="E110" s="33"/>
-      <c r="F110" s="33"/>
-      <c r="G110" s="29"/>
-      <c r="H110" s="29"/>
-      <c r="I110" s="29"/>
-    </row>
-    <row r="111" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="27">
-        <v>1</v>
-      </c>
-      <c r="B111" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="D111" s="33" t="s">
-        <v>13</v>
-      </c>
       <c r="E111" s="33"/>
-      <c r="F111" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="G111" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="H111" s="29" t="s">
-        <v>169</v>
-      </c>
+      <c r="F111" s="33"/>
+      <c r="G111" s="33"/>
+      <c r="H111" s="33"/>
       <c r="I111" s="29"/>
-    </row>
-    <row r="112" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J111" s="29"/>
+      <c r="K111" s="29"/>
+    </row>
+    <row r="112" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="27">
         <v>1</v>
       </c>
@@ -4625,79 +5066,91 @@
         <v>11</v>
       </c>
       <c r="C112" s="32" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D112" s="33" t="s">
         <v>13</v>
       </c>
       <c r="E112" s="33"/>
-      <c r="F112" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="G112" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="H112" s="29"/>
-      <c r="I112" s="29"/>
-    </row>
-    <row r="113" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F112" s="33"/>
+      <c r="G112" s="33"/>
+      <c r="H112" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="I112" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="J112" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="K112" s="29"/>
+    </row>
+    <row r="113" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="27">
         <v>1</v>
       </c>
       <c r="B113" s="32" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C113" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D113" s="33">
-        <v>0.99</v>
+        <v>163</v>
+      </c>
+      <c r="D113" s="33" t="s">
+        <v>13</v>
       </c>
       <c r="E113" s="33"/>
       <c r="F113" s="33"/>
-      <c r="G113" s="29"/>
-      <c r="H113" s="29"/>
-      <c r="I113" s="29"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="b">
+      <c r="G113" s="33"/>
+      <c r="H113" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="I113" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="J113" s="29"/>
+      <c r="K113" s="29"/>
+    </row>
+    <row r="114" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="27">
+        <v>1</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D114" s="33">
+        <v>0.99</v>
+      </c>
+      <c r="E114" s="33"/>
+      <c r="F114" s="33"/>
+      <c r="G114" s="33"/>
+      <c r="H114" s="33"/>
+      <c r="I114" s="29"/>
+      <c r="J114" s="29"/>
+      <c r="K114" s="29"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B115" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-    </row>
-    <row r="115" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="27">
-        <v>1</v>
-      </c>
-      <c r="B115" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C115" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="D115" s="33">
-        <v>0.65</v>
-      </c>
-      <c r="E115" s="33"/>
-      <c r="F115" s="33"/>
-      <c r="G115" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="H115" s="29"/>
-      <c r="I115" s="29"/>
-    </row>
-    <row r="116" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C115" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+    </row>
+    <row r="116" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="27">
         <v>1</v>
       </c>
@@ -4705,20 +5158,22 @@
         <v>21</v>
       </c>
       <c r="C116" s="32" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D116" s="33">
-        <v>1.3</v>
+        <v>0.65</v>
       </c>
       <c r="E116" s="33"/>
       <c r="F116" s="33"/>
-      <c r="G116" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="H116" s="29"/>
-      <c r="I116" s="29"/>
-    </row>
-    <row r="117" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G116" s="33"/>
+      <c r="H116" s="33"/>
+      <c r="I116" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="J116" s="29"/>
+      <c r="K116" s="29"/>
+    </row>
+    <row r="117" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="27">
         <v>1</v>
       </c>
@@ -4726,125 +5181,137 @@
         <v>21</v>
       </c>
       <c r="C117" s="32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D117" s="33">
-        <v>0.99</v>
+        <v>1.3</v>
       </c>
       <c r="E117" s="33"/>
       <c r="F117" s="33"/>
-      <c r="G117" s="29"/>
-      <c r="H117" s="29"/>
-      <c r="I117" s="29"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="b">
+      <c r="G117" s="33"/>
+      <c r="H117" s="33"/>
+      <c r="I117" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="J117" s="29"/>
+      <c r="K117" s="29"/>
+    </row>
+    <row r="118" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="27">
+        <v>1</v>
+      </c>
+      <c r="B118" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D118" s="33">
+        <v>0.99</v>
+      </c>
+      <c r="E118" s="33"/>
+      <c r="F118" s="33"/>
+      <c r="G118" s="33"/>
+      <c r="H118" s="33"/>
+      <c r="I118" s="29"/>
+      <c r="J118" s="29"/>
+      <c r="K118" s="29"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B119" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C119" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="6"/>
+    </row>
+    <row r="120" spans="1:11" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="27">
+        <v>0</v>
+      </c>
+      <c r="B120" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D120" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="33"/>
+      <c r="F120" s="33"/>
+      <c r="G120" s="33"/>
+      <c r="H120" s="33"/>
+      <c r="I120" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="J120" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="K120" s="29"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D121" s="6"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6"/>
+      <c r="G121" s="6"/>
+      <c r="H121" s="6"/>
+      <c r="I121" s="6"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="6"/>
+    </row>
+    <row r="122" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="25">
+        <v>1</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D122" s="25">
+        <v>76</v>
+      </c>
+      <c r="E122" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="F122" s="25">
+        <v>285</v>
+      </c>
+      <c r="G122" s="23"/>
+      <c r="H122" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="I122" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J122" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-    </row>
-    <row r="119" spans="1:9" s="30" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="27">
-        <v>0</v>
-      </c>
-      <c r="B119" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C119" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="D119" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" s="33"/>
-      <c r="F119" s="33"/>
-      <c r="G119" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="H119" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I119" s="29"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-    </row>
-    <row r="121" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="25">
-        <v>1</v>
-      </c>
-      <c r="B121" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C121" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="D121" s="25">
-        <v>76</v>
-      </c>
-      <c r="E121" s="23"/>
-      <c r="F121" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="G121" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="H121" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="I121" s="26"/>
-    </row>
-    <row r="122" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="25">
-        <v>1</v>
-      </c>
-      <c r="B122" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C122" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D122" s="25">
-        <v>0.88500000000000001</v>
-      </c>
-      <c r="E122" s="23"/>
-      <c r="F122" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="H122" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="I122" s="26"/>
-    </row>
-    <row r="123" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K122" s="26"/>
+    </row>
+    <row r="123" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="25">
         <v>1</v>
       </c>
@@ -4852,89 +5319,101 @@
         <v>21</v>
       </c>
       <c r="C123" s="26" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D123" s="25">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="E123" s="25"/>
+      <c r="F123" s="25"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="J123" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="K123" s="26"/>
+    </row>
+    <row r="124" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="25">
+        <v>1</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D124" s="25">
         <v>0.99</v>
       </c>
-      <c r="E123" s="23"/>
-      <c r="F123" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="26"/>
-      <c r="H123" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="I123" s="26"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="b">
+      <c r="E124" s="25"/>
+      <c r="F124" s="25"/>
+      <c r="G124" s="23"/>
+      <c r="H124" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="26"/>
+      <c r="J124" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="K124" s="26"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B125" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C124" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-    </row>
-    <row r="125" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="19">
-        <v>1</v>
-      </c>
-      <c r="B125" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C125" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="D125" s="19">
+      <c r="C125" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="6"/>
+    </row>
+    <row r="126" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="19">
+        <v>1</v>
+      </c>
+      <c r="B126" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C126" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D126" s="19">
         <v>74</v>
       </c>
-      <c r="E125" s="21"/>
-      <c r="F125" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="G125" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="H125" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I125" s="20"/>
-    </row>
-    <row r="126" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="19">
-        <v>1</v>
-      </c>
-      <c r="B126" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C126" s="20" t="s">
+      <c r="E126" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="F126" s="19">
+        <v>285</v>
+      </c>
+      <c r="G126" s="21"/>
+      <c r="H126" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="I126" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="J126" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="D126" s="19">
-        <v>0.88500000000000001</v>
-      </c>
-      <c r="E126" s="21"/>
-      <c r="F126" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="H126" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="I126" s="20"/>
-    </row>
-    <row r="127" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K126" s="20"/>
+    </row>
+    <row r="127" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19">
         <v>1</v>
       </c>
@@ -4942,572 +5421,740 @@
         <v>21</v>
       </c>
       <c r="C127" s="20" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D127" s="19">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="E127" s="19"/>
+      <c r="F127" s="19"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I127" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="J127" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="K127" s="20"/>
+    </row>
+    <row r="128" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="19">
+        <v>1</v>
+      </c>
+      <c r="B128" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D128" s="19">
         <v>0.99</v>
       </c>
-      <c r="E127" s="21"/>
-      <c r="F127" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
-    </row>
-    <row r="128" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="b">
+      <c r="E128" s="19"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" s="20"/>
+      <c r="J128" s="20"/>
+      <c r="K128" s="20"/>
+    </row>
+    <row r="129" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B129" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C129" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="6"/>
+      <c r="K129" s="6"/>
+    </row>
+    <row r="130" spans="1:11" s="24" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="25">
+        <v>1</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D130" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F130" s="34">
+        <v>70</v>
+      </c>
+      <c r="G130" s="23"/>
+      <c r="H130" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="I130" s="23"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="26"/>
+    </row>
+    <row r="131" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="25">
+        <v>1</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="D131" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F131" s="25">
+        <v>70</v>
+      </c>
+      <c r="G131" s="23"/>
+      <c r="H131" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="I131" s="23"/>
+      <c r="J131" s="26"/>
+      <c r="K131" s="26"/>
+    </row>
+    <row r="132" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="25">
+        <v>1</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="D132" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F132" s="25">
+        <v>70</v>
+      </c>
+      <c r="G132" s="23"/>
+      <c r="H132" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="I132" s="23"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="26"/>
+    </row>
+    <row r="133" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="25">
+        <v>1</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D133" s="25">
+        <v>0.94</v>
+      </c>
+      <c r="E133" s="25"/>
+      <c r="F133" s="25"/>
+      <c r="G133" s="23"/>
+      <c r="H133" s="26"/>
+      <c r="I133" s="26"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="23"/>
+    </row>
+    <row r="134" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="25">
+        <v>1</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D134" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F134" s="25">
+        <v>70</v>
+      </c>
+      <c r="G134" s="23"/>
+      <c r="H134" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-    </row>
-    <row r="129" spans="1:9" s="24" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="25">
-        <v>1</v>
-      </c>
-      <c r="B129" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C129" s="26" t="s">
+      <c r="I134" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="D129" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="23"/>
-      <c r="F129" s="23" t="s">
+      <c r="J134" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="G129" s="23"/>
-      <c r="H129" s="26"/>
-      <c r="I129" s="26"/>
-    </row>
-    <row r="130" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="25">
-        <v>1</v>
-      </c>
-      <c r="B130" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C130" s="26" t="s">
+      <c r="K134" s="26"/>
+    </row>
+    <row r="135" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="25">
+        <v>1</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="D130" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="23"/>
-      <c r="F130" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G130" s="23"/>
-      <c r="H130" s="26"/>
-      <c r="I130" s="26"/>
-    </row>
-    <row r="131" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="25">
-        <v>1</v>
-      </c>
-      <c r="B131" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C131" s="26" t="s">
+      <c r="D135" s="25">
+        <v>0.95</v>
+      </c>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25">
+        <v>70</v>
+      </c>
+      <c r="G135" s="23"/>
+      <c r="H135" s="23"/>
+      <c r="I135" s="23"/>
+      <c r="J135" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D131" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="23"/>
-      <c r="F131" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G131" s="23"/>
-      <c r="H131" s="26"/>
-      <c r="I131" s="26"/>
-    </row>
-    <row r="132" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="25">
-        <v>1</v>
-      </c>
-      <c r="B132" s="26" t="s">
+      <c r="K135" s="26"/>
+    </row>
+    <row r="136" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="25">
+        <v>1</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="D136" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F136" s="25">
+        <v>70</v>
+      </c>
+      <c r="G136" s="23"/>
+      <c r="H136" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="I136" s="23"/>
+      <c r="J136" s="24" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="25">
+        <v>1</v>
+      </c>
+      <c r="B137" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C132" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="D132" s="25">
+      <c r="C137" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D137" s="25">
+        <v>0.95</v>
+      </c>
+      <c r="E137" s="25"/>
+      <c r="F137" s="25"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="24" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="25">
+        <v>1</v>
+      </c>
+      <c r="B138" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="D138" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F138" s="25">
+        <v>70</v>
+      </c>
+      <c r="G138" s="23"/>
+      <c r="H138" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="I138" s="23"/>
+      <c r="J138" s="26"/>
+      <c r="K138" s="26"/>
+    </row>
+    <row r="139" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="25">
+        <v>1</v>
+      </c>
+      <c r="B139" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D139" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F139" s="25">
+        <v>70</v>
+      </c>
+      <c r="G139" s="23"/>
+      <c r="H139" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="I139" s="23"/>
+      <c r="J139" s="26"/>
+      <c r="K139" s="26"/>
+    </row>
+    <row r="140" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="25">
+        <v>1</v>
+      </c>
+      <c r="B140" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="D140" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F140" s="25">
+        <v>70</v>
+      </c>
+      <c r="G140" s="23"/>
+      <c r="H140" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="I140" s="23"/>
+      <c r="J140" s="26"/>
+      <c r="K140" s="26"/>
+    </row>
+    <row r="141" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="25">
+        <v>1</v>
+      </c>
+      <c r="B141" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C141" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D141" s="44">
+        <v>0.92</v>
+      </c>
+      <c r="E141" s="44"/>
+      <c r="F141" s="44"/>
+      <c r="G141" s="23"/>
+      <c r="H141" s="26"/>
+      <c r="I141" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="J141" s="24" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+      <c r="J142" s="6"/>
+      <c r="K142" s="6"/>
+    </row>
+    <row r="143" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="19">
+        <v>1</v>
+      </c>
+      <c r="B143" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D143" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F143" s="19">
+        <v>70</v>
+      </c>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="I143" s="21"/>
+      <c r="J143" s="20"/>
+      <c r="K143" s="20"/>
+    </row>
+    <row r="144" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="19">
+        <v>1</v>
+      </c>
+      <c r="B144" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D144" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="F144" s="22">
+        <v>70</v>
+      </c>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="I144" s="21"/>
+      <c r="J144" s="20"/>
+      <c r="K144" s="20"/>
+    </row>
+    <row r="145" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="19">
+        <v>1</v>
+      </c>
+      <c r="B145" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D145" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F145" s="19">
+        <v>70</v>
+      </c>
+      <c r="G145" s="21"/>
+      <c r="H145" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="I145" s="21"/>
+      <c r="J145" s="20"/>
+      <c r="K145" s="20"/>
+    </row>
+    <row r="146" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="19">
+        <v>1</v>
+      </c>
+      <c r="B146" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C146" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D146" s="19">
         <v>0.94</v>
       </c>
-      <c r="E132" s="23"/>
-      <c r="F132" s="26"/>
-      <c r="G132" s="26"/>
-      <c r="H132" s="23"/>
-      <c r="I132" s="23"/>
-    </row>
-    <row r="133" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="25">
-        <v>1</v>
-      </c>
-      <c r="B133" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C133" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="D133" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="23"/>
-      <c r="F133" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="G133" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="H133" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="I133" s="26"/>
-    </row>
-    <row r="134" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="25">
-        <v>1</v>
-      </c>
-      <c r="B134" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C134" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="D134" s="25">
-        <v>1</v>
-      </c>
-      <c r="E134" s="23"/>
-      <c r="F134" s="23"/>
-      <c r="G134" s="23"/>
-      <c r="H134" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="I134" s="26"/>
-    </row>
-    <row r="135" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="25">
-        <v>1</v>
-      </c>
-      <c r="B135" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C135" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="D135" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="23"/>
-      <c r="F135" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="G135" s="23"/>
-      <c r="H135" s="24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="25">
-        <v>1</v>
-      </c>
-      <c r="B136" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C136" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="D136" s="25">
-        <v>0.95</v>
-      </c>
-      <c r="E136" s="23"/>
-      <c r="F136" s="23"/>
-      <c r="G136" s="23"/>
-      <c r="H136" s="24" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="25">
-        <v>1</v>
-      </c>
-      <c r="B137" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C137" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="D137" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E137" s="23"/>
-      <c r="F137" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G137" s="23"/>
-      <c r="H137" s="26"/>
-      <c r="I137" s="26"/>
-    </row>
-    <row r="138" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="25">
-        <v>1</v>
-      </c>
-      <c r="B138" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C138" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="D138" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" s="23"/>
-      <c r="F138" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G138" s="23"/>
-      <c r="H138" s="26"/>
-      <c r="I138" s="26"/>
-    </row>
-    <row r="139" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="25">
-        <v>1</v>
-      </c>
-      <c r="B139" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C139" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="D139" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E139" s="23"/>
-      <c r="F139" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G139" s="23"/>
-      <c r="H139" s="26"/>
-      <c r="I139" s="26"/>
-    </row>
-    <row r="140" spans="1:9" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="25">
-        <v>1</v>
-      </c>
-      <c r="B140" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C140" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D140" s="46">
-        <v>0.92</v>
-      </c>
-      <c r="E140" s="23"/>
-      <c r="F140" s="26"/>
-      <c r="G140" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H140" s="24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-    </row>
-    <row r="142" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="19">
-        <v>1</v>
-      </c>
-      <c r="B142" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C142" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D142" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E142" s="21"/>
-      <c r="F142" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G142" s="21"/>
-      <c r="H142" s="20"/>
-      <c r="I142" s="20"/>
-    </row>
-    <row r="143" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="19">
-        <v>1</v>
-      </c>
-      <c r="B143" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C143" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="D143" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E143" s="21"/>
-      <c r="F143" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G143" s="21"/>
-      <c r="H143" s="20"/>
-      <c r="I143" s="20"/>
-    </row>
-    <row r="144" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="19">
-        <v>1</v>
-      </c>
-      <c r="B144" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C144" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="D144" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" s="21"/>
-      <c r="F144" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G144" s="21"/>
-      <c r="H144" s="20"/>
-      <c r="I144" s="20"/>
-    </row>
-    <row r="145" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="19">
-        <v>1</v>
-      </c>
-      <c r="B145" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C145" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="D145" s="19">
-        <v>0.94</v>
-      </c>
-      <c r="E145" s="21"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="21"/>
-      <c r="I145" s="21"/>
-    </row>
-    <row r="146" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="19">
-        <v>1</v>
-      </c>
-      <c r="B146" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C146" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D146" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E146" s="21"/>
-      <c r="F146" s="21" t="s">
-        <v>200</v>
-      </c>
+      <c r="E146" s="19"/>
+      <c r="F146" s="19"/>
       <c r="G146" s="21"/>
       <c r="H146" s="20"/>
       <c r="I146" s="20"/>
-    </row>
-    <row r="147" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J146" s="21"/>
+      <c r="K146" s="21"/>
+    </row>
+    <row r="147" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19">
         <v>1</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C147" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D147" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="E147" s="19"/>
+      <c r="F147" s="19"/>
+      <c r="G147" s="21"/>
+      <c r="H147" s="20"/>
+      <c r="I147" s="20"/>
+      <c r="J147" s="21"/>
+      <c r="K147" s="21"/>
+    </row>
+    <row r="148" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="19">
+        <v>1</v>
+      </c>
+      <c r="B148" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D148" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F148" s="19">
+        <v>70</v>
+      </c>
+      <c r="G148" s="21"/>
+      <c r="H148" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="I148" s="21"/>
+      <c r="J148" s="20"/>
+      <c r="K148" s="20"/>
+    </row>
+    <row r="149" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="19">
+        <v>1</v>
+      </c>
+      <c r="B149" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="D149" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F149" s="19">
+        <v>70</v>
+      </c>
+      <c r="G149" s="21"/>
+      <c r="H149" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="I149" s="21"/>
+      <c r="J149" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="K149" s="20"/>
+    </row>
+    <row r="150" spans="1:11" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="19">
+        <v>1</v>
+      </c>
+      <c r="B150" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C150" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D150" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="E150" s="19"/>
+      <c r="F150" s="19"/>
+      <c r="G150" s="21"/>
+      <c r="H150" s="21"/>
+      <c r="I150" s="21"/>
+      <c r="J150" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="K150" s="20"/>
+    </row>
+    <row r="151" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="19">
+        <v>1</v>
+      </c>
+      <c r="B151" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D151" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F151" s="19">
+        <v>70</v>
+      </c>
+      <c r="G151" s="21"/>
+      <c r="H151" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="I151" s="21"/>
+      <c r="J151" s="20"/>
+      <c r="K151" s="20"/>
+    </row>
+    <row r="152" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="19">
+        <v>1</v>
+      </c>
+      <c r="B152" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="D152" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F152" s="19">
+        <v>70</v>
+      </c>
+      <c r="G152" s="21"/>
+      <c r="H152" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="I152" s="21"/>
+      <c r="J152" s="20"/>
+      <c r="K152" s="20"/>
+    </row>
+    <row r="153" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="19">
+        <v>1</v>
+      </c>
+      <c r="B153" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="D147" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" s="21"/>
-      <c r="F147" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="G147" s="21"/>
-      <c r="H147" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="I147" s="20"/>
-    </row>
-    <row r="148" spans="1:9" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="19">
-        <v>1</v>
-      </c>
-      <c r="B148" s="20" t="s">
+      <c r="D153" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F153" s="19">
+        <v>70</v>
+      </c>
+      <c r="G153" s="21"/>
+      <c r="H153" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="I153" s="21"/>
+      <c r="J153" s="20"/>
+      <c r="K153" s="20"/>
+    </row>
+    <row r="154" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="19">
+        <v>1</v>
+      </c>
+      <c r="B154" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C148" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="D148" s="19">
-        <v>0.95</v>
-      </c>
-      <c r="E148" s="21"/>
-      <c r="F148" s="21"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="I148" s="20"/>
-    </row>
-    <row r="149" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="19">
-        <v>1</v>
-      </c>
-      <c r="B149" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C149" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D149" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="21"/>
-      <c r="F149" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G149" s="21"/>
-      <c r="H149" s="20"/>
-      <c r="I149" s="20"/>
-    </row>
-    <row r="150" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="19">
-        <v>1</v>
-      </c>
-      <c r="B150" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C150" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="D150" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E150" s="21"/>
-      <c r="F150" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G150" s="21"/>
-      <c r="H150" s="20"/>
-      <c r="I150" s="20"/>
-    </row>
-    <row r="151" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="19">
-        <v>1</v>
-      </c>
-      <c r="B151" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C151" s="20" t="s">
+      <c r="C154" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D154" s="44">
+        <v>0.98</v>
+      </c>
+      <c r="E154" s="44"/>
+      <c r="F154" s="44"/>
+      <c r="G154" s="21"/>
+      <c r="H154" s="20"/>
+      <c r="I154" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="J154" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="D151" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="21"/>
-      <c r="F151" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="G151" s="21"/>
-      <c r="H151" s="20"/>
-      <c r="I151" s="20"/>
-    </row>
-    <row r="152" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="19">
-        <v>1</v>
-      </c>
-      <c r="B152" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C152" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D152" s="46">
-        <v>0.98</v>
-      </c>
-      <c r="E152" s="21"/>
-      <c r="F152" s="20"/>
-      <c r="G152" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="H152" s="22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C153" s="1" t="s">
+      <c r="B155" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F153" s="1" t="s">
+      <c r="H155" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G153" s="1" t="s">
+      <c r="I155" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="J155" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I153" s="1"/>
+      <c r="K155" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G140" r:id="rId1" display="H4RG Options Summary" xr:uid="{C035A600-04E0-5A45-9DEB-9F1CAC882527}"/>
-    <hyperlink ref="G152" r:id="rId2" display="H4RG Options Summary" xr:uid="{0613B75C-56C8-6F48-B8E8-3ECD8427EBF5}"/>
-    <hyperlink ref="J50" r:id="rId3" xr:uid="{A654C731-D19C-4EE3-8FDC-41F0F8D77B59}"/>
+    <hyperlink ref="I141" r:id="rId1" display="H4RG Options Summary" xr:uid="{C035A600-04E0-5A45-9DEB-9F1CAC882527}"/>
+    <hyperlink ref="I154" r:id="rId2" display="H4RG Options Summary" xr:uid="{0613B75C-56C8-6F48-B8E8-3ECD8427EBF5}"/>
+    <hyperlink ref="L50" r:id="rId3" xr:uid="{A654C731-D19C-4EE3-8FDC-41F0F8D77B59}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
